--- a/Plotting/production_shares_olefins.xlsx
+++ b/Plotting/production_shares_olefins.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,9 @@
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -513,6 +516,13 @@
       </c>
       <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>noCO2electrolysis</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -580,6 +590,21 @@
           <t>2050</t>
         </is>
       </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -623,6 +648,15 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -666,6 +700,15 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -709,6 +752,15 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -752,6 +804,15 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -795,6 +856,15 @@
       <c r="M9" t="n">
         <v>728280.1200000008</v>
       </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -838,6 +908,15 @@
       <c r="M10" t="n">
         <v>1181399.88</v>
       </c>
+      <c r="N10" t="n">
+        <v>482062.0992000016</v>
+      </c>
+      <c r="O10" t="n">
+        <v>482062.099200021</v>
+      </c>
+      <c r="P10" t="n">
+        <v>350887.5359280714</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -881,6 +960,15 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
+      <c r="N11" t="n">
+        <v>1427617.900799999</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1304473.404382192</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1099742.632873076</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -924,12 +1012,22 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>123144.4964178076</v>
+      </c>
+      <c r="P12" t="n">
+        <v>327875.2679269238</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="B1:P1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>

--- a/Plotting/production_shares_olefins.xlsx
+++ b/Plotting/production_shares_olefins.xlsx
@@ -504,21 +504,21 @@
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>MPWemission</t>
+          <t>noCO2electrolysis</t>
         </is>
       </c>
       <c r="I2" s="1" t="n"/>
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>OptBIO</t>
+          <t>MPWemission</t>
         </is>
       </c>
       <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="n"/>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>noCO2electrolysis</t>
+          <t>OptBIO</t>
         </is>
       </c>
       <c r="O2" s="1" t="n"/>
@@ -842,28 +842,28 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>653899.105228933</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>834670.9833528211</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>496209.4965803243</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>728280.1200000008</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -891,31 +891,31 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1181399.88</v>
+        <v>482062.0992000016</v>
       </c>
       <c r="I10" t="n">
-        <v>1181100.694501541</v>
+        <v>482062.099200021</v>
       </c>
       <c r="J10" t="n">
-        <v>1075009.016647179</v>
+        <v>350887.5359280714</v>
       </c>
       <c r="K10" t="n">
         <v>1181399.88</v>
       </c>
       <c r="L10" t="n">
+        <v>1181100.694501541</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1075009.016647179</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1181399.88</v>
+      </c>
+      <c r="O10" t="n">
         <v>1120395.893280752</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
         <v>1181399.88</v>
-      </c>
-      <c r="N10" t="n">
-        <v>482062.0992000016</v>
-      </c>
-      <c r="O10" t="n">
-        <v>482062.099200021</v>
-      </c>
-      <c r="P10" t="n">
-        <v>350887.5359280714</v>
       </c>
     </row>
     <row r="11">
@@ -943,31 +943,31 @@
         <v>243883.9464986075</v>
       </c>
       <c r="H11" t="n">
+        <v>1427617.900799999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1304473.404382192</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1099742.632873076</v>
+      </c>
+      <c r="K11" t="n">
         <v>728280.1199999312</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>9095.797163709341</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>728280.1200000007</v>
       </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>293074.6101389172</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1427617.900799999</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1304473.404382192</v>
-      </c>
       <c r="P11" t="n">
-        <v>1099742.632873076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -998,17 +998,17 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>123144.4964178076</v>
+      </c>
+      <c r="J12" t="n">
+        <v>327875.2679269238</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>65584.40310581523</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1016,10 +1016,10 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>123144.4964178076</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>327875.2679269238</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
